--- a/quizzes/028_hiragana_recognition_quiz--quizzes.xlsx
+++ b/quizzes/028_hiragana_recognition_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>quiz_1</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hiragana_Sheet</t>
+          <t>How many Hiragana letters do you recognize?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>quiz_2</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hiragana_Sheet</t>
+          <t>Which Hiragana letter represents the sound /a/?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>quiz_3</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hiragana_Sheet</t>
+          <t>How often do you practice writing Hiragana characters?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,20 +584,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>quiz_4</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is your favorite Hiragana character?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please specify your favorite Hiragana character.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,17 +611,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>quiz_5</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hiragana_Sheet</t>
+          <t>What is your level of proficiency in reading Hiragana?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +634,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>quiz_6</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hiragana_Sheet</t>
+          <t>What is your favorite resource for learning Hiragana?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +657,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>quiz_7</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hiragana_Sheet</t>
+          <t>Have you used Hiragana in a professional setting?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +680,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>quiz_8</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hiragana_Sheet</t>
+          <t>When did you start learning Hiragana?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +703,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>quiz_9</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hiragana_Sheet</t>
+          <t>How would you rate your knowledge of Hiragana?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,15 +731,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>quiz_10</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What motivates you to learn Hiragana?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please specify your motivation for learning Hiragana.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,12 +758,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>quiz_11</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hiragana_Sheet</t>
+          <t>How long does it take to learn Hiragana?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,315 +781,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>quiz_12</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hiragana_Sheet</t>
+          <t>Do you prefer learning Hiragana from a book or online resources?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>quiz_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>quiz_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>quiz_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>quiz_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>quiz_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>quiz_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>quiz_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>quiz_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>quiz_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>quiz_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>quiz_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>quiz_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>quiz_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Hiragana_Sheet</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +807,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,340 +835,442 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quiz_3_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>1._1-5_letters</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1. 1-5 letters</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quiz_3_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>2._6-10_letters</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2. 6-10 letters</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quiz_11_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>3._more_than_10_letters</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>3. More than 10 letters</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quiz_11_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quiz_12_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>ka</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Ka</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quiz_12_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other (Please specify)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quiz_14_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quiz_14_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quiz_20_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quiz_20_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quiz_21_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>quiz_21_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>quiz_22_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>online_courses</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Online courses</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>quiz_22_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>practice_apps</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Practice apps</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>quiz_23_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>books</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Books</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>quiz_23_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>quiz_24_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>quiz_24_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>quiz_25_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>quiz_25_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>less_than_a_month</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Less than a month</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>several_months</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Several months</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>more_than_a_year</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>More than a year</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>online_resources</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Online resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Both</t>
         </is>
       </c>
     </row>
